--- a/artfynd/A 40395-2025 artfynd.xlsx
+++ b/artfynd/A 40395-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1318,6 +1318,567 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128757591</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91477</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1205</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Stor aspticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Phellinus populicola</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kubbolbacke, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>653658</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6674689</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128757566</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57683</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kubbolbacke, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>653741</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6674647</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128757605</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92784</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kubbolbacke, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>653675</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6674625</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Bara gran inom 10 m håll. En tall ca 15 m bort. Annars bara asp, utöver granar.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128757579</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58059</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kubbolbacke, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>653759</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6674652</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128757583</v>
+      </c>
+      <c r="B11" t="n">
+        <v>81074</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kubbolbacke, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>653680</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6674643</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40395-2025 artfynd.xlsx
+++ b/artfynd/A 40395-2025 artfynd.xlsx
@@ -1323,7 +1323,7 @@
         <v>128757591</v>
       </c>
       <c r="B7" t="n">
-        <v>91477</v>
+        <v>91478</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>128757605</v>
       </c>
       <c r="B9" t="n">
-        <v>92784</v>
+        <v>92785</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 40395-2025 artfynd.xlsx
+++ b/artfynd/A 40395-2025 artfynd.xlsx
@@ -1323,7 +1323,7 @@
         <v>128757591</v>
       </c>
       <c r="B7" t="n">
-        <v>91478</v>
+        <v>91505</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>128757566</v>
       </c>
       <c r="B8" t="n">
-        <v>57683</v>
+        <v>57710</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>128757605</v>
       </c>
       <c r="B9" t="n">
-        <v>92785</v>
+        <v>92812</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>128757579</v>
       </c>
       <c r="B10" t="n">
-        <v>58059</v>
+        <v>58086</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>128757583</v>
       </c>
       <c r="B11" t="n">
-        <v>81074</v>
+        <v>81101</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 40395-2025 artfynd.xlsx
+++ b/artfynd/A 40395-2025 artfynd.xlsx
@@ -1323,7 +1323,7 @@
         <v>128757591</v>
       </c>
       <c r="B7" t="n">
-        <v>91505</v>
+        <v>91510</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>128757605</v>
       </c>
       <c r="B9" t="n">
-        <v>92812</v>
+        <v>92817</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>128757583</v>
       </c>
       <c r="B11" t="n">
-        <v>81101</v>
+        <v>81105</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 40395-2025 artfynd.xlsx
+++ b/artfynd/A 40395-2025 artfynd.xlsx
@@ -1323,7 +1323,7 @@
         <v>128757591</v>
       </c>
       <c r="B7" t="n">
-        <v>91510</v>
+        <v>91515</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>128757605</v>
       </c>
       <c r="B9" t="n">
-        <v>92817</v>
+        <v>92823</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1558,21 +1558,12 @@
       <c r="E9" t="n">
         <v>5449</v>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Svart taggsvamp</t>
-        </is>
-      </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>

--- a/artfynd/A 40395-2025 artfynd.xlsx
+++ b/artfynd/A 40395-2025 artfynd.xlsx
@@ -1323,7 +1323,7 @@
         <v>128757591</v>
       </c>
       <c r="B7" t="n">
-        <v>91515</v>
+        <v>91519</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>128757566</v>
       </c>
       <c r="B8" t="n">
-        <v>57710</v>
+        <v>57714</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>128757605</v>
       </c>
       <c r="B9" t="n">
-        <v>92823</v>
+        <v>92827</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>128757579</v>
       </c>
       <c r="B10" t="n">
-        <v>58086</v>
+        <v>58090</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>128757583</v>
       </c>
       <c r="B11" t="n">
-        <v>81105</v>
+        <v>81109</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 40395-2025 artfynd.xlsx
+++ b/artfynd/A 40395-2025 artfynd.xlsx
@@ -1323,7 +1323,7 @@
         <v>128757591</v>
       </c>
       <c r="B7" t="n">
-        <v>91519</v>
+        <v>91524</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>128757566</v>
       </c>
       <c r="B8" t="n">
-        <v>57714</v>
+        <v>57717</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>128757605</v>
       </c>
       <c r="B9" t="n">
-        <v>92827</v>
+        <v>92832</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>128757579</v>
       </c>
       <c r="B10" t="n">
-        <v>58090</v>
+        <v>58093</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>128757583</v>
       </c>
       <c r="B11" t="n">
-        <v>81109</v>
+        <v>81014</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 40395-2025 artfynd.xlsx
+++ b/artfynd/A 40395-2025 artfynd.xlsx
@@ -1323,7 +1323,7 @@
         <v>128757591</v>
       </c>
       <c r="B7" t="n">
-        <v>91531</v>
+        <v>91534</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>128757605</v>
       </c>
       <c r="B9" t="n">
-        <v>92840</v>
+        <v>92845</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 40395-2025 artfynd.xlsx
+++ b/artfynd/A 40395-2025 artfynd.xlsx
@@ -1323,7 +1323,7 @@
         <v>128757591</v>
       </c>
       <c r="B7" t="n">
-        <v>91534</v>
+        <v>91537</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>128757605</v>
       </c>
       <c r="B9" t="n">
-        <v>92845</v>
+        <v>92848</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>128757583</v>
       </c>
       <c r="B11" t="n">
-        <v>81019</v>
+        <v>81020</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 40395-2025 artfynd.xlsx
+++ b/artfynd/A 40395-2025 artfynd.xlsx
@@ -1323,7 +1323,7 @@
         <v>128757591</v>
       </c>
       <c r="B7" t="n">
-        <v>91537</v>
+        <v>91544</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>128757566</v>
       </c>
       <c r="B8" t="n">
-        <v>57717</v>
+        <v>57719</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>128757605</v>
       </c>
       <c r="B9" t="n">
-        <v>92848</v>
+        <v>92855</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>128757579</v>
       </c>
       <c r="B10" t="n">
-        <v>58093</v>
+        <v>58095</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>128757583</v>
       </c>
       <c r="B11" t="n">
-        <v>81020</v>
+        <v>81024</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 40395-2025 artfynd.xlsx
+++ b/artfynd/A 40395-2025 artfynd.xlsx
@@ -1323,7 +1323,7 @@
         <v>128757591</v>
       </c>
       <c r="B7" t="n">
-        <v>91544</v>
+        <v>91553</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>128757566</v>
       </c>
       <c r="B8" t="n">
-        <v>57719</v>
+        <v>57721</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>128757605</v>
       </c>
       <c r="B9" t="n">
-        <v>92855</v>
+        <v>92864</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>128757579</v>
       </c>
       <c r="B10" t="n">
-        <v>58095</v>
+        <v>58097</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>128757583</v>
       </c>
       <c r="B11" t="n">
-        <v>81024</v>
+        <v>81026</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
